--- a/stories/arbres/TREE-DIF-003.xlsx
+++ b/stories/arbres/TREE-DIF-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à la maison, avec papa. Maman prépare le goûter. Un copain a des lunettes. Une copine a les cheveux courts. Un habit est neuf. Papa dit : pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Hugo est à la maison, avec papa. Maman prépare le goûter. Un copain a des lunettes. Une copine a les cheveux courts. Un habit est neuf. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est à la maison, avec papa. Maman prépare le goûter. Un copain a des lunettes. Une copine a les cheveux courts. Un habit est neuf.
+papa|Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo prend le ballon rouge. Un copain a des lunettes. Hugo passe le ballon. Pas rire de l'apparence. Ils jouent ensemble. Papa dit : les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
+          <t>Hugo prend le ballon rouge. Un copain a des lunettes. Hugo passe le ballon. Pas rire de l'apparence. Ils jouent ensemble. Les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo prend le ballon rouge. Un copain a des lunettes. Hugo passe le ballon. Pas rire de l'apparence. Ils jouent ensemble.
+papa|Les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On rit des lunettes ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo respire. Maman est là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2225,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe le ballon à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils jouent ensemble. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon rouge. Puis Tom. Puis le matin. Une tasse cliquette. Hugo écoute maman encore une fois. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Hugo range la tasse. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo se souvient de le ballon rouge. Et de Tom. Et de le soir. Une cloche tinte, tout loin. Hugo répète tout bas le geste. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3616,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hugo passe le ballon à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils jouent ensemble. Maman dit : je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Hugo passe le ballon à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils jouent ensemble. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3754,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe le ballon à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils jouent ensemble.
+maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3946,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4113,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Hugo s'arrête. Les chaussures font toc toc. Hugo pose sa tête un moment. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range Léa. après la sieste reste près de le ballon rouge. On se tient la main. Hugo chuchote : c'est fini. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4643,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe le ballon à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils jouent ensemble. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le ballon rouge est fini. Une feuille tombe. Hugo plie un pull. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Hugo pose Sami. le ballon rouge est derrière. Un linge sèche à l'air. Papa n'est pas loin. Hugo les rejoint. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo montre le soir. Maman a vu le ballon rouge. Et Sami. La lumière est claire. Hugo prend la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6475,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo prend le seau bleu. Une copine a les cheveux très courts. Hugo lui tend le seau. Pas rire de l'apparence. Ils mettent des pinces dedans. Maman apporte l'eau. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6660,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Pas rire de l'apparence. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6833,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo retient le geste. Maman sourit. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7028,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7057,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Hugo tend le seau à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils remplissent le seau. Maman dit : je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Hugo tend le seau à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils remplissent le seau. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7195,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo tend le seau à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils remplissent le seau.
+maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7387,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7554,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau bleu. Puis Tom. Puis le matin. Un panier est posé sur le banc. Hugo essuie ses mains. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7721,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7888,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. On attend son tour. Hugo range encore un peu, près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8055,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8222,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo se souvient de le seau bleu. Et de Tom. Et de le soir. Un chat miaule une fois. Hugo ferme la porte, tout doux. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8389,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8556,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo tend le seau à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils portent le seau. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8747,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8914,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Hugo s'arrête. L'eau coule, tout petit bruit. Hugo montre le matin à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9081,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9248,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range Léa. après la sieste reste près de le seau bleu. Le vent est doux. Hugo pose Léa à sa place. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9415,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9444,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9582,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9749,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9916,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo tend le seau à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils vident le seau. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10107,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10274,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le seau bleu est fini. Un ruban reste dans la poche. Hugo ferme le sac. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10441,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10608,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Hugo pose Sami. le seau bleu est derrière. Une chaussette est encore sablée. Hugo caresse le doudou. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10775,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10942,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo montre le soir. Maman a vu le seau bleu. Et Sami. Le savon sent bon. Hugo marche près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11109,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11138,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo prend le doudou. Un copain porte un habit trop grand. Hugo dit : on joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
+          <t>Hugo prend le doudou. Un copain porte un habit trop grand. On joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11276,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo prend le doudou. Un copain porte un habit trop grand.
+enfant-m|On joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On joue, sans rire de l'habit ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo hoche la tête. On continue, avec maman. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11497,6 +11824,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11661,6 +11993,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo confie le doudou à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils asseyent le doudou. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12184,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12351,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Puis Tom. Puis le matin. On dit merci. Hugo raccroche un linge. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12518,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12685,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un galet est encore chaud. Hugo s'assoit près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12852,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13019,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo se souvient de le doudou. Et de Tom. Et de le soir. La couverture est douce. Hugo dit merci à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13353,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo confie le doudou à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils le bercent. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13544,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13711,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Hugo s'arrête. Le sol est un peu froid. Hugo sourit. Maman sourit aussi. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13878,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14045,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range Léa. après la sieste reste près de le doudou. On range un objet. Hugo range le doudou dans sa tête, comme un souvenir. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14212,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13839,7 +14241,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13977,6 +14379,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14546,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14163,7 +14575,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo confie le doudou à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils le couvrent. Maman dit : je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Hugo confie le doudou à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils le couvrent. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14301,6 +14713,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo confie le doudou à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils le couvrent.
+maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14905,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15072,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le doudou est fini. On écoute jusqu'au bout. Hugo tend le matin à papa. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15239,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14835,7 +15268,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Hugo pose Sami. le doudou est derrière. On rit un peu. Hugo dit : j'ai appris. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Près de après la sieste. Hugo pose Sami. le doudou est derrière. On rit un peu. J'ai appris. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14973,6 +15406,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Hugo pose Sami. le doudou est derrière. On rit un peu.
+enfant-m|J'ai appris. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire.
+narrateur|Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15575,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15742,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo montre le soir. Maman a vu le doudou. Et Sami. Un ballon s'immobilise. Hugo serre la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15909,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15508,6 +15963,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-003.xlsx
+++ b/stories/arbres/TREE-DIF-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 papa|Les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|On rit des lunettes ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo respire. Maman est là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Hugo passe le ballon à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils jouent ensemble. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Hugo a choisi le ballon rouge. Puis Tom. Puis le matin. Une tasse cliquette. Hugo écoute maman encore une fois. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Hugo range la tasse. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Hugo se souvient de le ballon rouge. Et de Tom. Et de le soir. Une cloche tinte, tout loin. Hugo répète tout bas le geste. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
 maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3951,6 +3971,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4118,6 +4139,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Hugo s'arrête. Les chaussures font toc toc. Hugo pose sa tête un moment. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4475,7 @@
           <t>narrateur|Hugo range Léa. après la sieste reste près de le ballon rouge. On se tient la main. Hugo chuchote : c'est fini. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4811,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
           <t>narrateur|Hugo passe le ballon à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils jouent ensemble. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5478,6 +5507,7 @@
           <t>narrateur|Hugo rejoint le matin. Sami est rangé. le ballon rouge est fini. Une feuille tombe. Hugo plie un pull. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5843,7 @@
           <t>narrateur|Près de après la sieste. Hugo pose Sami. le ballon rouge est derrière. Un linge sèche à l'air. Papa n'est pas loin. Hugo les rejoint. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6179,7 @@
           <t>narrateur|Hugo montre le soir. Maman a vu le ballon rouge. Et Sami. La lumière est claire. Hugo prend la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6480,6 +6515,7 @@
           <t>narrateur|Hugo prend le seau bleu. Une copine a les cheveux très courts. Hugo lui tend le seau. Pas rire de l'apparence. Ils mettent des pinces dedans. Maman apporte l'eau. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6667,6 +6703,7 @@
           <t>narrateur|Pas rire de l'apparence. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6838,6 +6875,7 @@
           <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo retient le geste. Maman sourit. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7033,6 +7071,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7201,6 +7240,7 @@
 maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7559,6 +7600,7 @@
           <t>narrateur|Hugo a choisi le seau bleu. Puis Tom. Puis le matin. Un panier est posé sur le banc. Hugo essuie ses mains. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7726,6 +7768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7893,6 +7936,7 @@
           <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. On attend son tour. Hugo range encore un peu, près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8060,6 +8104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8227,6 +8272,7 @@
           <t>narrateur|Hugo se souvient de le seau bleu. Et de Tom. Et de le soir. Un chat miaule une fois. Hugo ferme la porte, tout doux. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8394,6 +8440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8561,6 +8608,7 @@
           <t>narrateur|Hugo tend le seau à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils portent le seau. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8752,6 +8800,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8919,6 +8968,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Hugo s'arrête. L'eau coule, tout petit bruit. Hugo montre le matin à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9086,6 +9136,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9253,6 +9304,7 @@
           <t>narrateur|Hugo range Léa. après la sieste reste près de le seau bleu. Le vent est doux. Hugo pose Léa à sa place. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9420,6 +9472,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9587,6 +9640,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9754,6 +9808,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9921,6 +9976,7 @@
           <t>narrateur|Hugo tend le seau à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils vident le seau. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10112,6 +10168,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10279,6 +10336,7 @@
           <t>narrateur|Hugo rejoint le matin. Sami est rangé. le seau bleu est fini. Un ruban reste dans la poche. Hugo ferme le sac. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10446,6 +10504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10613,6 +10672,7 @@
           <t>narrateur|Près de après la sieste. Hugo pose Sami. le seau bleu est derrière. Une chaussette est encore sablée. Hugo caresse le doudou. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10780,6 +10840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10947,6 +11008,7 @@
           <t>narrateur|Hugo montre le soir. Maman a vu le seau bleu. Et Sami. Le savon sent bon. Hugo marche près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11114,6 +11176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,7 @@
 enfant-m|On joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11529,7 @@
           <t>narrateur|On joue, sans rire de l'habit ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11701,7 @@
           <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo hoche la tête. On continue, avec maman. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11831,6 +11897,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11998,6 +12065,7 @@
           <t>narrateur|Hugo confie le doudou à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils asseyent le doudou. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12189,6 +12257,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12356,6 +12425,7 @@
           <t>narrateur|Hugo a choisi le doudou. Puis Tom. Puis le matin. On dit merci. Hugo raccroche un linge. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12523,6 +12593,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12690,6 +12761,7 @@
           <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un galet est encore chaud. Hugo s'assoit près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12857,6 +12929,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13024,6 +13097,7 @@
           <t>narrateur|Hugo se souvient de le doudou. Et de Tom. Et de le soir. La couverture est douce. Hugo dit merci à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13191,6 +13265,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13358,6 +13433,7 @@
           <t>narrateur|Hugo confie le doudou à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils le bercent. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13549,6 +13625,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13716,6 +13793,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Hugo s'arrête. Le sol est un peu froid. Hugo sourit. Maman sourit aussi. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13883,6 +13961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14050,6 +14129,7 @@
           <t>narrateur|Hugo range Léa. après la sieste reste près de le doudou. On range un objet. Hugo range le doudou dans sa tête, comme un souvenir. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14217,6 +14297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14384,6 +14465,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14551,6 +14633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14719,6 +14802,7 @@
 maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14910,6 +14994,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15077,6 +15162,7 @@
           <t>narrateur|Hugo rejoint le matin. Sami est rangé. le doudou est fini. On écoute jusqu'au bout. Hugo tend le matin à papa. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15244,6 +15330,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15413,6 +15500,7 @@
 narrateur|Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15580,6 +15668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15747,6 +15836,7 @@
           <t>narrateur|Hugo montre le soir. Maman a vu le doudou. Et Sami. Un ballon s'immobilise. Hugo serre la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15914,6 +16004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15932,7 +16023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15970,6 +16061,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15984,7 +16089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16171,6 +16276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-003.xlsx
+++ b/stories/arbres/TREE-DIF-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lunettes, cheveux, habit — à la maison</t>
+          <t>Le manteau à pois et les lunettes de Mila</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte tombe du manteau à pois. Nina invite Mila. On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à la maison, avec papa. Maman prépare le goûter. Un copain a des lunettes. Une copine a les cheveux courts. Un habit est neuf. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Les chaussons de Nina font chut sur le carrelage. Un manteau à pois brille au crochet. Une goutte tombe du bas, sur le paillasson. Elle fait ploc, tout petit. Maman tourne la cuillère dans le bol. Ça sent le pain grillé. Papa plie un torchon, près de l'évier. Le radiateur fait un tic doux. Tu as entendu le ploc, Nina ? Oui. C'est le manteau. Il sèche, tout doux. En ce moment, Nina est dans le salon. Le tapis a un fil rouge qui dépasse. Mila arrive avec son sac. Mila a des lunettes rondes. Elles brillent un peu. Mila a les cheveux courts. Son habit à pois est neuf. On joue ensemble. On ne rit pas de l'apparence. On joue. On joue. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. Le crochet cliquette un peu, tout seul. Le bol de maman fume encore, tout loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,41 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est à la maison, avec papa. Maman prépare le goûter. Un copain a des lunettes. Une copine a les cheveux courts. Un habit est neuf.
-papa|Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les chaussons de Nina font chut sur le carrelage.
+narrateur|Un manteau à pois brille au crochet.
+narrateur|Une goutte tombe du bas, sur le paillasson.
+narrateur|Elle fait ploc, tout petit.
+narrateur|Maman tourne la cuillère dans le bol.
+narrateur|Ça sent le pain grillé.
+narrateur|Papa plie un torchon, près de l'évier.
+narrateur|Le radiateur fait un tic doux.
+maman|Tu as entendu le ploc, Nina ?
+enfant-f|Oui.
+enfant-f|C'est le manteau.
+papa|Il sèche, tout doux.
+narrateur|En ce moment, Nina est dans le salon.
+narrateur|Le tapis a un fil rouge qui dépasse.
+narrateur|Mila arrive avec son sac.
+narrateur|Mila a des lunettes rondes.
+narrateur|Elles brillent un peu.
+narrateur|Mila a les cheveux courts.
+narrateur|Son habit à pois est neuf.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+enfant-f|On joue.
+copine|On joue.
+papa|Les lunettes aident à voir.
+papa|Les cheveux sont les cheveux.
+papa|L'habit tient chaud.
+narrateur|Le crochet cliquette un peu, tout seul.
+narrateur|Le bol de maman fume encore, tout loin.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,assiette</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On joue ensemble.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1560,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo prend le ballon rouge. Un copain a des lunettes. Hugo passe le ballon. Pas rire de l'apparence. Ils jouent ensemble. Les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
+          <t>Nina prend le ballon rouge. Le ballon est un peu tiède, tout lisse. Il fait poum contre le sol. Mila a des lunettes rondes. Elles brillent un peu. Tu veux le ballon ? Oui. Nina passe le ballon, tout doux. Les lunettes aident à voir. On ne rit pas de l'apparence. On joue ensemble. On joue. On joue. Le ballon va, puis revient. Bravo, Nina. Tu as invité Mila. C'est du bon travail. Une perle de lumière glisse sur une lunette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,11 +1730,31 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo prend le ballon rouge. Un copain a des lunettes. Hugo passe le ballon. Pas rire de l'apparence. Ils jouent ensemble.
-papa|Les lunettes aident à voir. On joue. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon rouge.
+narrateur|Le ballon est un peu tiède, tout lisse.
+narrateur|Il fait poum contre le sol.
+narrateur|Mila a des lunettes rondes.
+narrateur|Elles brillent un peu.
+enfant-f|Tu veux le ballon ?
+copine|Oui.
+narrateur|Nina passe le ballon, tout doux.
+maman|Les lunettes aident à voir.
+maman|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+enfant-f|On joue.
+copine|On joue.
+narrateur|Le ballon va, puis revient.
+maman|Bravo, Nina.
+maman|Tu as invité Mila.
+papa|C'est du bon travail.
+narrateur|Une perle de lumière glisse sur une lunette.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1715,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On rit des lunettes ?</t>
+          <t>Mila a des lunettes. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1935,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On rit des lunettes ?</t>
+          <t>narrateur|Mila a des lunettes.
+maman|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Pas rire de l'apparence. On joue. Hugo respire. Maman est là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue. On ne rit pas de l'apparence. Nina souffle un peu. Le ballon reste chaud contre son ventre. On joue. Bravo, Nina. Tu as fait du bon travail. Les lunettes restent bien sur le nez.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2108,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo respire. Maman est là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On joue.
+maman|On ne rit pas de l'apparence.
+narrateur|Nina souffle un peu.
+narrateur|Le ballon reste chaud contre son ventre.
+enfant-f|On joue.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Les lunettes restent bien sur le nez.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2144,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins de la maison attendent. Le tapis, le canapé, ou le carton ? On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2239,7 +2312,10 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|Le tapis, le canapé, ou le carton ?
+papa|On joue.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2267,7 +2343,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hugo passe le ballon à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils jouent ensemble. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina s'assoit sur le tapis. Le tapis est épais, un peu rêche. Un fil rouge dépasse, tout petit. Mila s'assoit en face, tout près. On joue ici ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. Elles posent le jeu au milieu du tapis. C'est doux. Bravo. Vous êtes bien, là. Le ballon fait un creux, au milieu du tapis. On a encore le ballon rouge. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2407,7 +2483,24 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Hugo passe le ballon à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils jouent ensemble. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina s'assoit sur le tapis.
+narrateur|Le tapis est épais, un peu rêche.
+narrateur|Un fil rouge dépasse, tout petit.
+narrateur|Mila s'assoit en face, tout près.
+enfant-f|On joue ici ?
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|Les lunettes aident à voir.
+papa|Les cheveux sont les cheveux.
+narrateur|Elles posent le jeu au milieu du tapis.
+enfant-f|C'est doux.
+maman|Bravo.
+maman|Vous êtes bien, là.
+narrateur|Le ballon fait un creux, au milieu du tapis.
+narrateur|On a encore le ballon rouge.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2435,7 +2528,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2599,7 +2692,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2627,7 +2722,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon rouge. Puis Tom. Puis le matin. Une tasse cliquette. Hugo écoute maman encore une fois. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le tapis. Mila est encore là, tout près. Le ballon rouge attrape le soleil, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2767,10 +2862,35 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon rouge. Puis Tom. Puis le matin. Une tasse cliquette. Hugo écoute maman encore une fois. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le ballon rouge attrape le soleil, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2795,7 +2915,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le tapis. Elle a joué avec le ballon rouge, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2935,7 +3055,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le tapis.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2963,7 +3091,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Hugo range la tasse. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le ballon rouge, près de le tapis. Mila est encore là, tout près. Le ballon est tiède, comme les joues, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3103,7 +3231,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un crochet tient bien le manteau. Hugo range la tasse. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le ballon rouge, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le ballon est tiède, comme les joues, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3131,7 +3280,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le tapis. Elle a joué avec le ballon rouge, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3271,7 +3420,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le tapis.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3299,7 +3456,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hugo se souvient de le ballon rouge. Et de Tom. Et de le soir. Une cloche tinte, tout loin. Hugo répète tout bas le geste. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le tapis. Mila est encore là, tout près. L'ombre du ballon danse sur le tapis, sous la lampe. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3439,10 +3596,35 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Hugo se souvient de le ballon rouge. Et de Tom. Et de le soir. Une cloche tinte, tout loin. Hugo répète tout bas le geste. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|L'ombre du ballon danse sur le tapis, sous la lampe.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3467,7 +3649,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le tapis. Elle a joué avec le ballon rouge, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3607,7 +3789,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le tapis.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3635,7 +3825,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hugo passe le ballon à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils jouent ensemble. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina grimpe sur le canapé. Le tissu est chaud, un peu lourd. Un coussin a une tache de lumière. Mila s'assoit à côté, tout calme. Vous avez de la place ? Oui. Oui. On joue ensemble. On ne rit pas de l'apparence. L'habit tient chaud. Elles posent le jeu entre les genoux. On est bien. Bravo, Nina. Tu as fait une place à Mila. Le ballon roule jusqu'au coussin, tout lentement. On a encore le ballon rouge. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3775,8 +3965,24 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Hugo passe le ballon à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils jouent ensemble.
-maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina grimpe sur le canapé.
+narrateur|Le tissu est chaud, un peu lourd.
+narrateur|Un coussin a une tache de lumière.
+narrateur|Mila s'assoit à côté, tout calme.
+papa|Vous avez de la place ?
+enfant-f|Oui.
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|L'habit tient chaud.
+narrateur|Elles posent le jeu entre les genoux.
+enfant-f|On est bien.
+maman|Bravo, Nina.
+maman|Tu as fait une place à Mila.
+narrateur|Le ballon roule jusqu'au coussin, tout lentement.
+narrateur|On a encore le ballon rouge.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3804,7 +4010,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3968,7 +4174,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3996,7 +4204,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le ballon rouge. Hugo s'arrête. Les chaussures font toc toc. Hugo pose sa tête un moment. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le canapé. Mila est encore là, tout près. Le ballon rouge brille contre le coussin clair. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4136,10 +4344,35 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Hugo s'arrête. Les chaussures font toc toc. Hugo pose sa tête un moment. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le ballon rouge brille contre le coussin clair.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4164,7 +4397,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le canapé. Elle a joué avec le ballon rouge, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4304,7 +4537,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le canapé.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4332,7 +4573,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Hugo range Léa. après la sieste reste près de le ballon rouge. On se tient la main. Hugo chuchote : c'est fini. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le ballon rouge, près de le canapé. Mila est encore là, tout près. Le ballon s'enfonce un peu, dans le canapé chaud. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4472,7 +4713,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Hugo range Léa. après la sieste reste près de le ballon rouge. On se tient la main. Hugo chuchote : c'est fini. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le ballon rouge, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le ballon s'enfonce un peu, dans le canapé chaud.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4500,7 +4762,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le canapé. Elle a joué avec le ballon rouge, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4640,7 +4902,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le canapé.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4668,7 +4938,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le canapé. Mila est encore là, tout près. La lampe allonge l'ombre du ballon, sur le canapé. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4808,10 +5078,35 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Hugo souffle, puis sourit à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|La lampe allonge l'ombre du ballon, sur le canapé.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4836,7 +5131,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le canapé. Elle a joué avec le ballon rouge, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4976,7 +5271,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le canapé.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5004,7 +5307,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hugo passe le ballon à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils jouent ensemble. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina ouvre le carton. Le carton sent le papier, un peu sec. Un rabat fait un bruit tout creux. Mila tient l'autre rabat, tout doux. C'est une maison ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes restent bien en place. L'habit à pois brille un peu. Elles mettent le jeu dans le carton. On rentre. Bravo. Vous jouez. Le ballon rentre dans le carton, trop juste. On a encore le ballon rouge. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5144,10 +5447,31 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Hugo passe le ballon à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils jouent ensemble. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nina ouvre le carton.
+narrateur|Le carton sent le papier, un peu sec.
+narrateur|Un rabat fait un bruit tout creux.
+narrateur|Mila tient l'autre rabat, tout doux.
+enfant-f|C'est une maison ?
+copine|Oui.
+papa|On joue ensemble.
+papa|On ne rit pas de l'apparence.
+maman|Les lunettes restent bien en place.
+maman|L'habit à pois brille un peu.
+narrateur|Elles mettent le jeu dans le carton.
+enfant-f|On rentre.
+papa|Bravo.
+papa|Vous jouez.
+narrateur|Le ballon rentre dans le carton, trop juste.
+narrateur|On a encore le ballon rouge.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>carton</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5172,7 +5496,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5336,7 +5660,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5364,7 +5690,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le matin. Sami est rangé. le ballon rouge est fini. Une feuille tombe. Hugo plie un pull. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le carton. Mila est encore là, tout près. Un rabat du carton a un rond de soleil, tout jaune. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5504,10 +5830,35 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le ballon rouge est fini. Une feuille tombe. Hugo plie un pull. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Un rabat du carton a un rond de soleil, tout jaune.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5532,7 +5883,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le carton. Elle a joué avec le ballon rouge, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5672,7 +6023,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le carton.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5700,7 +6059,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Hugo pose Sami. le ballon rouge est derrière. Un linge sèche à l'air. Papa n'est pas loin. Hugo les rejoint. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le ballon rouge, près de le carton. Mila est encore là, tout près. Le ballon est calme, dans le carton un peu sombre. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5840,7 +6199,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Hugo pose Sami. le ballon rouge est derrière. Un linge sèche à l'air. Papa n'est pas loin. Hugo les rejoint. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le ballon rouge, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le ballon est calme, dans le carton un peu sombre.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5868,7 +6248,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le carton. Elle a joué avec le ballon rouge, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6008,7 +6388,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le carton.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6036,7 +6424,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Hugo montre le soir. Maman a vu le ballon rouge. Et Sami. La lumière est claire. Hugo prend la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le ballon rouge, près de le carton. Mila est encore là, tout près. La lampe éclaire l'intérieur du carton, tout doux. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le ballon rouge, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6176,10 +6564,35 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Hugo montre le soir. Maman a vu le ballon rouge. Et Sami. La lumière est claire. Hugo prend la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le ballon rouge, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|La lampe éclaire l'intérieur du carton, tout doux.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le ballon rouge, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6204,7 +6617,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le carton. Elle a joué avec le ballon rouge, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6344,7 +6757,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le carton.
+narrateur|Elle a joué avec le ballon rouge, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6372,7 +6793,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo prend le seau bleu. Une copine a les cheveux très courts. Hugo lui tend le seau. Pas rire de l'apparence. Ils mettent des pinces dedans. Maman apporte l'eau. On peut jouer ensemble.</t>
+          <t>Nina prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Mila a les cheveux très courts. Ils sont doux, tout près des oreilles. On met des pinces ? Oui. Elles mettent des pinces dans le seau. Les cheveux sont les cheveux. On ne rit pas de l'apparence. On joue ensemble. Maman apporte un peu d'eau. Merci, maman. Bravo. Vous jouez. Une pince rouge flotte, tout légère. Elle brille. On joue.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6512,10 +6933,31 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Hugo prend le seau bleu. Une copine a les cheveux très courts. Hugo lui tend le seau. Pas rire de l'apparence. Ils mettent des pinces dedans. Maman apporte l'eau. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+narrateur|Mila a les cheveux très courts.
+narrateur|Ils sont doux, tout près des oreilles.
+enfant-f|On met des pinces ?
+copine|Oui.
+narrateur|Elles mettent des pinces dans le seau.
+maman|Les cheveux sont les cheveux.
+maman|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+papa|Maman apporte un peu d'eau.
+enfant-f|Merci, maman.
+maman|Bravo.
+maman|Vous jouez.
+narrateur|Une pince rouge flotte, tout légère.
+copine|Elle brille.
+papa|On joue.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6540,7 +6982,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Pas rire de l'apparence. On fait quoi ?</t>
+          <t>Mila a les cheveux courts. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6700,7 +7142,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Pas rire de l'apparence. On fait quoi ?</t>
+          <t>narrateur|Mila a les cheveux courts.
+papa|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6728,7 +7171,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Pas rire de l'apparence. On joue. Hugo retient le geste. Maman sourit. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue. On ne rit pas de l'apparence. Nina essuie une goutte sur le seau. Le plastique est un peu froid. On joue. Bravo. Les cheveux sont les cheveux. Une pince rouge reste au fond, tout sage.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6872,7 +7315,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo retient le geste. Maman sourit. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On joue.
+papa|On ne rit pas de l'apparence.
+narrateur|Nina essuie une goutte sur le seau.
+narrateur|Le plastique est un peu froid.
+enfant-f|On joue.
+maman|Bravo.
+maman|Les cheveux sont les cheveux.
+narrateur|Une pince rouge reste au fond, tout sage.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6900,7 +7351,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins de la maison attendent. Le tapis, le canapé, ou le carton ? On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7068,7 +7519,10 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|Le tapis, le canapé, ou le carton ?
+papa|On joue.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7096,7 +7550,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Hugo tend le seau à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils remplissent le seau. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina s'assoit sur le tapis. Le tapis est épais, un peu rêche. Un fil rouge dépasse, tout petit. Mila s'assoit en face, tout près. On joue ici ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. Elles posent le jeu au milieu du tapis. C'est doux. Bravo. Vous êtes bien, là. Le seau laisse un rond mouillé, sur le tapis. On a encore le seau bleu. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7236,8 +7690,24 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Hugo tend le seau à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils remplissent le seau.
-maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina s'assoit sur le tapis.
+narrateur|Le tapis est épais, un peu rêche.
+narrateur|Un fil rouge dépasse, tout petit.
+narrateur|Mila s'assoit en face, tout près.
+enfant-f|On joue ici ?
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|Les lunettes aident à voir.
+papa|Les cheveux sont les cheveux.
+narrateur|Elles posent le jeu au milieu du tapis.
+enfant-f|C'est doux.
+maman|Bravo.
+maman|Vous êtes bien, là.
+narrateur|Le seau laisse un rond mouillé, sur le tapis.
+narrateur|On a encore le seau bleu.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7265,7 +7735,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7429,7 +7899,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7457,7 +7929,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau bleu. Puis Tom. Puis le matin. Un panier est posé sur le banc. Hugo essuie ses mains. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le tapis. Mila est encore là, tout près. Une goutte du seau brille, sur le fil rouge du tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7597,10 +8069,35 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau bleu. Puis Tom. Puis le matin. Un panier est posé sur le banc. Hugo essuie ses mains. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Une goutte du seau brille, sur le fil rouge du tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7625,7 +8122,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le tapis. Elle a joué avec le seau bleu, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7765,7 +8262,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le tapis.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7793,7 +8298,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'arrête près de après la sieste. Tom est rangé. On attend son tour. Hugo range encore un peu, près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le seau bleu, près de le tapis. Mila est encore là, tout près. Le seau bleu est tiède, posé sur le tapis calme. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7933,7 +8438,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. On attend son tour. Hugo range encore un peu, près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le seau bleu, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le seau bleu est tiède, posé sur le tapis calme.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7961,7 +8487,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le tapis. Elle a joué avec le seau bleu, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8101,7 +8627,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le tapis.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8129,7 +8663,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Hugo se souvient de le seau bleu. Et de Tom. Et de le soir. Un chat miaule une fois. Hugo ferme la porte, tout doux. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le tapis. Mila est encore là, tout près. Le seau bleu reflète la lampe, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8269,10 +8803,35 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Hugo se souvient de le seau bleu. Et de Tom. Et de le soir. Un chat miaule une fois. Hugo ferme la porte, tout doux. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le seau bleu reflète la lampe, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8297,7 +8856,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le tapis. Elle a joué avec le seau bleu, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8437,7 +8996,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le tapis.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8465,7 +9032,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hugo tend le seau à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils portent le seau. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina grimpe sur le canapé. Le tissu est chaud, un peu lourd. Un coussin a une tache de lumière. Mila s'assoit à côté, tout calme. Vous avez de la place ? Oui. Oui. On joue ensemble. On ne rit pas de l'apparence. L'habit tient chaud. Elles posent le jeu entre les genoux. On est bien. Bravo, Nina. Tu as fait une place à Mila. Le seau attend au pied du canapé, tout sage. On a encore le seau bleu. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8605,7 +9172,24 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Hugo tend le seau à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils portent le seau. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina grimpe sur le canapé.
+narrateur|Le tissu est chaud, un peu lourd.
+narrateur|Un coussin a une tache de lumière.
+narrateur|Mila s'assoit à côté, tout calme.
+papa|Vous avez de la place ?
+enfant-f|Oui.
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|L'habit tient chaud.
+narrateur|Elles posent le jeu entre les genoux.
+enfant-f|On est bien.
+maman|Bravo, Nina.
+maman|Tu as fait une place à Mila.
+narrateur|Le seau attend au pied du canapé, tout sage.
+narrateur|On a encore le seau bleu.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8633,7 +9217,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8797,7 +9381,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8825,7 +9411,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le seau bleu. Hugo s'arrête. L'eau coule, tout petit bruit. Hugo montre le matin à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le canapé. Mila est encore là, tout près. Le seau attend au pied du canapé, dans le soleil. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8965,10 +9551,35 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Hugo s'arrête. L'eau coule, tout petit bruit. Hugo montre le matin à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le seau attend au pied du canapé, dans le soleil.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8993,7 +9604,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le canapé. Elle a joué avec le seau bleu, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9133,7 +9744,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le canapé.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9161,7 +9780,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hugo range Léa. après la sieste reste près de le seau bleu. Le vent est doux. Hugo pose Léa à sa place. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le seau bleu, près de le canapé. Mila est encore là, tout près. Une pince tremble encore, près du canapé tiède. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9301,7 +9920,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Hugo range Léa. après la sieste reste près de le seau bleu. Le vent est doux. Hugo pose Léa à sa place. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le seau bleu, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Une pince tremble encore, près du canapé tiède.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9329,7 +9969,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le canapé. Elle a joué avec le seau bleu, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9469,7 +10109,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le canapé.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9497,7 +10145,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le canapé. Mila est encore là, tout près. Le seau sonne un tout petit ding, sous la lampe. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9637,10 +10285,35 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un vélo passe au loin. Hugo boit une gorgée d'eau. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le seau sonne un tout petit ding, sous la lampe.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9665,7 +10338,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le canapé. Elle a joué avec le seau bleu, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9805,7 +10478,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le canapé.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9833,7 +10514,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Hugo tend le seau à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils vident le seau. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina ouvre le carton. Le carton sent le papier, un peu sec. Un rabat fait un bruit tout creux. Mila tient l'autre rabat, tout doux. C'est une maison ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes restent bien en place. L'habit à pois brille un peu. Elles mettent le jeu dans le carton. On rentre. Bravo. Vous jouez. Le seau sonne contre le carton, tout creux. On a encore le seau bleu. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9973,10 +10654,31 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Hugo tend le seau à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils vident le seau. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nina ouvre le carton.
+narrateur|Le carton sent le papier, un peu sec.
+narrateur|Un rabat fait un bruit tout creux.
+narrateur|Mila tient l'autre rabat, tout doux.
+enfant-f|C'est une maison ?
+copine|Oui.
+papa|On joue ensemble.
+papa|On ne rit pas de l'apparence.
+maman|Les lunettes restent bien en place.
+maman|L'habit à pois brille un peu.
+narrateur|Elles mettent le jeu dans le carton.
+enfant-f|On rentre.
+papa|Bravo.
+papa|Vous jouez.
+narrateur|Le seau sonne contre le carton, tout creux.
+narrateur|On a encore le seau bleu.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>carton</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10001,7 +10703,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10165,7 +10867,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10193,7 +10897,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le matin. Sami est rangé. le seau bleu est fini. Un ruban reste dans la poche. Hugo ferme le sac. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le carton. Mila est encore là, tout près. Le seau bleu a un reflet de matin, dans le carton. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10333,10 +11037,35 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le seau bleu est fini. Un ruban reste dans la poche. Hugo ferme le sac. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le seau bleu a un reflet de matin, dans le carton.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10361,7 +11090,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le carton. Elle a joué avec le seau bleu, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10501,7 +11230,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le carton.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10529,7 +11266,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Hugo pose Sami. le seau bleu est derrière. Une chaussette est encore sablée. Hugo caresse le doudou. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le seau bleu, près de le carton. Mila est encore là, tout près. Une goutte sèche au bord du carton, tout calme. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10669,7 +11406,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Hugo pose Sami. le seau bleu est derrière. Une chaussette est encore sablée. Hugo caresse le doudou. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le seau bleu, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Une goutte sèche au bord du carton, tout calme.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10697,7 +11455,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le carton. Elle a joué avec le seau bleu, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10837,7 +11595,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le carton.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10865,7 +11631,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Hugo montre le soir. Maman a vu le seau bleu. Et Sami. Le savon sent bon. Hugo marche près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le seau bleu, près de le carton. Mila est encore là, tout près. Le carton sent encore l'eau, près de la lampe. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le seau bleu, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11005,10 +11771,35 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Hugo montre le soir. Maman a vu le seau bleu. Et Sami. Le savon sent bon. Hugo marche près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le seau bleu, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le carton sent encore l'eau, près de la lampe.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le seau bleu, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11033,7 +11824,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le carton. Elle a joué avec le seau bleu, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11173,7 +11964,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le carton.
+narrateur|Elle a joué avec le seau bleu, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11201,7 +12000,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo prend le doudou. Un copain porte un habit trop grand. On joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
+          <t>Nina prend le doudou. Le doudou est gris, un peu chaud. Une oreille est froissée. Mila porte un habit à pois, tout neuf. Les pois sont blancs, sur le bleu. On assied le doudou ? Oui. Elles asseyent le doudou contre un coussin. L'habit tient chaud. On ne rit pas de l'apparence. On joue ensemble. Je plie une manche, tout doux. Merci, papa. Bravo, Nina. Tu as partagé le doudou. Le doudou a une place, tout calme. Il dort. On joue.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11341,8 +12140,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Hugo prend le doudou. Un copain porte un habit trop grand.
-enfant-m|On joue. Pas rire de l'apparence. Ils asseyent le doudou. Papa plie une manche, tout doux. On peut jouer ensemble.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Le doudou est gris, un peu chaud.
+narrateur|Une oreille est froissée.
+narrateur|Mila porte un habit à pois, tout neuf.
+narrateur|Les pois sont blancs, sur le bleu.
+enfant-f|On assied le doudou ?
+copine|Oui.
+narrateur|Elles asseyent le doudou contre un coussin.
+papa|L'habit tient chaud.
+papa|On ne rit pas de l'apparence.
+maman|On joue ensemble.
+papa|Je plie une manche, tout doux.
+enfant-f|Merci, papa.
+maman|Bravo, Nina.
+maman|Tu as partagé le doudou.
+narrateur|Le doudou a une place, tout calme.
+copine|Il dort.
+papa|On joue.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11370,7 +12185,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On joue, sans rire de l'habit ?</t>
+          <t>Mila a un habit à pois. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11526,7 +12341,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On joue, sans rire de l'habit ?</t>
+          <t>narrateur|Mila a un habit à pois.
+maman|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11554,7 +12370,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Pas rire de l'apparence. On joue. Hugo hoche la tête. On continue, avec maman. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue. On ne rit pas de l'apparence. Nina hoche la tête. Le doudou a encore l'oreille froissée. On joue. Bravo. L'habit tient chaud. Un pois blanc attrape la lumière.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11698,7 +12514,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Pas rire de l'apparence. On joue. Hugo hoche la tête. On continue, avec maman. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On joue.
+maman|On ne rit pas de l'apparence.
+narrateur|Nina hoche la tête.
+narrateur|Le doudou a encore l'oreille froissée.
+enfant-f|On joue.
+papa|Bravo.
+papa|L'habit tient chaud.
+narrateur|Un pois blanc attrape la lumière.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11726,7 +12550,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins de la maison attendent. Le tapis, le canapé, ou le carton ? On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11894,7 +12718,10 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|Le tapis, le canapé, ou le carton ?
+papa|On joue.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11922,7 +12749,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Hugo confie le doudou à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils asseyent le doudou. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina s'assoit sur le tapis. Le tapis est épais, un peu rêche. Un fil rouge dépasse, tout petit. Mila s'assoit en face, tout près. On joue ici ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. Elles posent le jeu au milieu du tapis. C'est doux. Bravo. Vous êtes bien, là. Le doudou s'allonge sur le tapis, l'oreille à plat. On a encore le doudou. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12062,7 +12889,24 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Hugo confie le doudou à Tom. Tom a des lunettes. Pas rire de l'apparence. Ils asseyent le doudou. Maman reste tout près. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina s'assoit sur le tapis.
+narrateur|Le tapis est épais, un peu rêche.
+narrateur|Un fil rouge dépasse, tout petit.
+narrateur|Mila s'assoit en face, tout près.
+enfant-f|On joue ici ?
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|Les lunettes aident à voir.
+papa|Les cheveux sont les cheveux.
+narrateur|Elles posent le jeu au milieu du tapis.
+enfant-f|C'est doux.
+maman|Bravo.
+maman|Vous êtes bien, là.
+narrateur|Le doudou s'allonge sur le tapis, l'oreille à plat.
+narrateur|On a encore le doudou.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12090,7 +12934,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12254,7 +13098,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12282,7 +13128,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. Puis Tom. Puis le matin. On dit merci. Hugo raccroche un linge. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le doudou, près de le tapis. Mila est encore là, tout près. L'oreille du doudou a un rond de soleil, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12422,10 +13268,35 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. Puis Tom. Puis le matin. On dit merci. Hugo raccroche un linge. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|L'oreille du doudou a un rond de soleil, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12450,7 +13321,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le tapis. Elle a joué avec le doudou, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12590,7 +13461,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le tapis.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12618,7 +13497,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'arrête près de après la sieste. Tom est rangé. Un galet est encore chaud. Hugo s'assoit près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le doudou, près de le tapis. Mila est encore là, tout près. Le doudou est chaud, comme la couverture, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12758,7 +13637,28 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'arrête près de après la sieste. Tom est rangé. Un galet est encore chaud. Hugo s'assoit près de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le doudou, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou est chaud, comme la couverture, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12786,7 +13686,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le tapis. Elle a joué avec le doudou, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12926,7 +13826,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le tapis.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12954,7 +13862,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Hugo se souvient de le doudou. Et de Tom. Et de le soir. La couverture est douce. Hugo dit merci à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le doudou, près de le tapis. Mila est encore là, tout près. Le doudou a une ombre longue, sur le tapis. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13094,10 +14002,35 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Hugo se souvient de le doudou. Et de Tom. Et de le soir. La couverture est douce. Hugo dit merci à maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le tapis.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou a une ombre longue, sur le tapis.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13122,7 +14055,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le tapis. Elle a joué avec le doudou, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13262,7 +14195,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le tapis.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13290,7 +14231,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Hugo confie le doudou à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils le bercent. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina grimpe sur le canapé. Le tissu est chaud, un peu lourd. Un coussin a une tache de lumière. Mila s'assoit à côté, tout calme. Vous avez de la place ? Oui. Oui. On joue ensemble. On ne rit pas de l'apparence. L'habit tient chaud. Elles posent le jeu entre les genoux. On est bien. Bravo, Nina. Tu as fait une place à Mila. Le doudou a une place, contre le coussin. On a encore le doudou. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13430,7 +14371,24 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Hugo confie le doudou à Léa. Léa a un habit à pois. Pas rire de l'apparence. Ils le bercent. Maman montre le geste, lentement. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Nina grimpe sur le canapé.
+narrateur|Le tissu est chaud, un peu lourd.
+narrateur|Un coussin a une tache de lumière.
+narrateur|Mila s'assoit à côté, tout calme.
+papa|Vous avez de la place ?
+enfant-f|Oui.
+copine|Oui.
+maman|On joue ensemble.
+maman|On ne rit pas de l'apparence.
+papa|L'habit tient chaud.
+narrateur|Elles posent le jeu entre les genoux.
+enfant-f|On est bien.
+maman|Bravo, Nina.
+maman|Tu as fait une place à Mila.
+narrateur|Le doudou a une place, contre le coussin.
+narrateur|On a encore le doudou.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13458,7 +14416,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13622,7 +14580,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13650,7 +14610,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le doudou. Hugo s'arrête. Le sol est un peu froid. Hugo sourit. Maman sourit aussi. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le doudou, près de le canapé. Mila est encore là, tout près. Le doudou s'adosse au coussin, dans la lumière. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13790,10 +14750,35 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Hugo s'arrête. Le sol est un peu froid. Hugo sourit. Maman sourit aussi. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou s'adosse au coussin, dans la lumière.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13818,7 +14803,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le canapé. Elle a joué avec le doudou, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13958,7 +14943,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le canapé.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13986,7 +14979,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hugo range Léa. après la sieste reste près de le doudou. On range un objet. Hugo range le doudou dans sa tête, comme un souvenir. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le doudou, près de le canapé. Mila est encore là, tout près. Le doudou garde le pli de la sieste, sur le canapé. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14126,7 +15119,28 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Hugo range Léa. après la sieste reste près de le doudou. On range un objet. Hugo range le doudou dans sa tête, comme un souvenir. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le doudou, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou garde le pli de la sieste, sur le canapé.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14154,7 +15168,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le canapé. Elle a joué avec le doudou, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14294,7 +15308,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le canapé.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14322,7 +15344,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le doudou, près de le canapé. Mila est encore là, tout près. Le doudou reflète la lampe, contre le coussin. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14462,10 +15484,35 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On entend un oiseau. Hugo enfile ses chaussons. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le canapé.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou reflète la lampe, contre le coussin.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14490,7 +15537,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le canapé. Elle a joué avec le doudou, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14630,7 +15677,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le canapé.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14658,7 +15713,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo confie le doudou à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils le couvrent. Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Nina ouvre le carton. Le carton sent le papier, un peu sec. Un rabat fait un bruit tout creux. Mila tient l'autre rabat, tout doux. C'est une maison ? Oui. On joue ensemble. On ne rit pas de l'apparence. Les lunettes restent bien en place. L'habit à pois brille un peu. Elles mettent le jeu dans le carton. On rentre. Bravo. Vous jouez. Le doudou s'assoit dans le carton, tout calme. On a encore le doudou. On joue ensemble. On ne rit pas de l'apparence.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14798,11 +15853,31 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Hugo confie le doudou à Sami. Sami a les cheveux collés. Pas rire de l'apparence. Ils le couvrent.
-maman|Je suis là. Pas rire de l'apparence. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nina ouvre le carton.
+narrateur|Le carton sent le papier, un peu sec.
+narrateur|Un rabat fait un bruit tout creux.
+narrateur|Mila tient l'autre rabat, tout doux.
+enfant-f|C'est une maison ?
+copine|Oui.
+papa|On joue ensemble.
+papa|On ne rit pas de l'apparence.
+maman|Les lunettes restent bien en place.
+maman|L'habit à pois brille un peu.
+narrateur|Elles mettent le jeu dans le carton.
+enfant-f|On rentre.
+papa|Bravo.
+papa|Vous jouez.
+narrateur|Le doudou s'assoit dans le carton, tout calme.
+narrateur|On a encore le doudou.
+maman|On joue ensemble.
+papa|On ne rit pas de l'apparence.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>carton</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14827,7 +15902,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14991,7 +16066,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15019,7 +16096,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le matin. Sami est rangé. le doudou est fini. On écoute jusqu'au bout. Hugo tend le matin à papa. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le matin, le bol de cacao fume encore. Un rai de soleil traverse le rideau. Les chaussons sont encore un peu froids. Bonjour, Nina. Bonjour, papa. Nina a encore le doudou, près de le carton. Mila est encore là, tout près. Le doudou cligne, dans le carton clair du matin. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15159,10 +16236,35 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint le matin. Sami est rangé. le doudou est fini. On écoute jusqu'au bout. Hugo tend le matin à papa. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, le bol de cacao fume encore.
+narrateur|Un rai de soleil traverse le rideau.
+narrateur|Les chaussons sont encore un peu froids.
+papa|Bonjour, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou cligne, dans le carton clair du matin.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15187,7 +16289,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le matin, près de le carton. Elle a joué avec le doudou, et avec Mila. Le bol de cacao ne fume plus, près du rideau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15327,7 +16429,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le matin, près de le carton.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le bol de cacao ne fume plus, près du rideau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15355,7 +16465,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Hugo pose Sami. le doudou est derrière. On rit un peu. J'ai appris. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Après la sieste, un oreiller a un creux. Le radiateur fait encore tic, tout petit. Ça sent le linge chaud. Tu es réveillée ? Oui, maman. Nina a encore le doudou, près de le carton. Mila est encore là, tout près. Le doudou s'endort encore un peu, dans le carton. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15495,9 +16605,28 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Hugo pose Sami. le doudou est derrière. On rit un peu.
-enfant-m|J'ai appris. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire.
-narrateur|Hugo dit merci à maman.</t>
+          <t>narrateur|Après la sieste, un oreiller a un creux.
+narrateur|Le radiateur fait encore tic, tout petit.
+narrateur|Ça sent le linge chaud.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Nina a encore le doudou, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le doudou s'endort encore un peu, dans le carton.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15525,7 +16654,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu après la sieste, près de le carton. Elle a joué avec le doudou, et avec Mila. L'oreiller garde encore son creux, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15665,7 +16794,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu après la sieste, près de le carton.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|L'oreiller garde encore son creux, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15693,7 +16830,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hugo montre le soir. Maman a vu le doudou. Et Sami. Un ballon s'immobilise. Hugo serre la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
+          <t>Le soir, la lampe fait un rond jaune. Le pain craque, tout loin, dans la cuisine. Un chausson attend sous la table. Te voilà, Nina. Bonjour, papa. Nina a encore le doudou, près de le carton. Mila est encore là, tout près. Le carton devient une maison, sous la lampe. On joue encore ? Oui. Oui. On ne rit pas de l'apparence. On joue ensemble. Les lunettes aident à voir. Les cheveux sont les cheveux. Merci, Mila. Merci, Nina. Bravo. C'est du bon travail. Nina range le doudou, tout doux. Tu as fini de ranger un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15833,10 +16970,35 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Hugo montre le soir. Maman a vu le doudou. Et Sami. Un ballon s'immobilise. Hugo serre la main de maman. Pas rire de l'apparence. On joue ensemble. On joue. Pas rire. Hugo dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond jaune.
+narrateur|Le pain craque, tout loin, dans la cuisine.
+narrateur|Un chausson attend sous la table.
+papa|Te voilà, Nina.
+enfant-f|Bonjour, papa.
+narrateur|Nina a encore le doudou, près de le carton.
+narrateur|Mila est encore là, tout près.
+narrateur|Le carton devient une maison, sous la lampe.
+maman|On joue encore ?
+enfant-f|Oui.
+copine|Oui.
+papa|On ne rit pas de l'apparence.
+papa|On joue ensemble.
+maman|Les lunettes aident à voir.
+maman|Les cheveux sont les cheveux.
+enfant-f|Merci, Mila.
+copine|Merci, Nina.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Nina range le doudou, tout doux.
+maman|Tu as fini de ranger un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15861,7 +17023,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a joué. On ne rit pas de l'apparence. Bravo, Nina. Tu as fait du bon travail. Nina a vécu le soir, près de le carton. Elle a joué avec le doudou, et avec Mila. Le chausson sous la table n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16001,7 +17163,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+copine|On a joué.
+maman|On ne rit pas de l'apparence.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a vécu le soir, près de le carton.
+narrateur|Elle a joué avec le doudou, et avec Mila.
+narrateur|Le chausson sous la table n'attend plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16023,7 +17193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16075,6 +17245,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-003.xlsx
+++ b/stories/arbres/TREE-DIF-003.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un éclat de thym colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois.</t>
+          <t>La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. La casserole frémit, près du thym. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un éclat de thym colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un &lt;emphasis level="moderate"&gt;éclat de thym&lt;/emphasis&gt; colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. La casserole frémit, près du thym. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un &lt;emphasis level="moderate"&gt;éclat de thym&lt;/emphasis&gt; colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un &lt;emphasis&gt;éclat de thym&lt;/emphasis&gt; colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois. [pause]</t>
+          <t>La gouttière compte, goutte après goutte. Mila compte avec elle, dans la cuisine. Ça sent le poireau, et le thym coupé. La casserole frémit, près du thym. Un nuage de soupe cache la vitre. Je fais un rond, pour voir. Papa essuie, et le seuil apparaît. Le manteau à pois goutte, au crochet. Un &lt;emphasis&gt;éclat de thym&lt;/emphasis&gt; colle à un pois. Il n'était pas là, ce matin. C'est le thym de la soupe. En ce moment, Mila touche le pois. Je sors, avant la dernière goutte. Elle veut le manteau, et les lunettes. Le seau attend sous l'évier. Aniss pousse la porte, sans un mot. Il s'arrête, et regarde l'éclat. On y va, Aniss. Aniss ne dit rien. Merci, tu as attendu sa voix. Le thym, moi je le vois. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1344,6 +1344,7 @@
           <t>narrateur|La gouttière compte, goutte après goutte.
 narrateur|Mila compte avec elle, dans la cuisine.
 narrateur|Ça sent le poireau, et le thym coupé.
+narrateur|La casserole frémit, près du thym.
 narrateur|Un nuage de soupe cache la vitre.
 papa|Je fais un rond, pour voir.
 narrateur|Papa essuie, et le seuil apparaît.
@@ -1968,17 +1969,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, sur un pois.</t>
+          <t>Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, sur un pois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, sur un pois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, sur un pois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, sur un pois. [pause]</t>
+          <t>Le manteau reste sur elle, un peu lourd. La feuille est dans la poche. Les lunettes tiennent, Mila ? Oui, sur mon nez. Le seau, Aniss le tient. J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, sur un pois. [pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2120,6 +2121,8 @@
 enfant-m|J'ai l'anse.
 narrateur|Ils avancent vers le seuil, sans courir.
 maman|La gouttière n'a pas fini.
+enfant-f|Une maison, avant la dernière goutte.
+narrateur|Aniss marche derrière, sans se presser.
 narrateur|Un éclat de thym brille, sur un pois.</t>
         </is>
       </c>
@@ -7249,17 +7252,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Les lunettes restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord d'un verre.</t>
+          <t>Les lunettes restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord d'un verre.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt; restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord d'un verre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt; restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord d'un verre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Les &lt;emphasis&gt;lunettes&lt;/emphasis&gt; restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord d'un verre. [pause]</t>
+          <t>Les &lt;emphasis&gt;lunettes&lt;/emphasis&gt; restent nettes, sur son nez. Je vois le seuil, dehors. Le manteau te tient chaud ? Oui, il est un peu lourd. Aniss, tu tiens le seau ? J'ai l'anse. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord d'un verre. [pause]</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -7401,6 +7404,8 @@
 enfant-m|J'ai l'anse.
 narrateur|Ils avancent vers le seuil, sans courir.
 papa|La gouttière n'a pas fini.
+enfant-f|Une maison, avant la dernière goutte.
+narrateur|Aniss marche derrière, sans se presser.
 narrateur|Un éclat de thym brille, au bord d'un verre.</t>
         </is>
       </c>
@@ -12150,17 +12155,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Mila attrape le seau sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ?</t>
+          <t>Mila attrape le seau sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ? Oui.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila attrape le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ?&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila attrape le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ? Oui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Mila attrape le &lt;emphasis&gt;seau&lt;/emphasis&gt; sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ? [pause]</t>
+          <t>Mila attrape le &lt;emphasis&gt;seau&lt;/emphasis&gt; sous l'évier. Il sonne creux, comme un petit tambour. Il est coincé ! Je tire, moi. Aniss pose les deux mains, et attend. Mila veut tirer trop fort, trop vite. Deux mains, et on glisse. Le seau se libère, d'un coup. C'est l'hôtel. Une feuille, et une goutte ? Mila pose une feuille sèche, au fond. Le manteau, et les lunettes aussi ? Oui, on les prend. Je porte l'anse. Le seau se balance, puis se tient. L'hôtel est prêt ? Oui. [pause]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -12309,7 +12314,8 @@
 enfant-f|Oui, on les prend.
 enfant-m|Je porte l'anse.
 narrateur|Le seau se balance, puis se tient.
-maman|L'hôtel est prêt ?</t>
+maman|L'hôtel est prêt ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -12529,17 +12535,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord du seau.</t>
+          <t>La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord du seau.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord du &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord du &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Un éclat de thym brille, au bord du &lt;emphasis&gt;seau&lt;/emphasis&gt;. [pause]</t>
+          <t>La feuille nage dans sa goutte, au fond. L'hôtel voyage. Deux mains sur l'anse, Aniss. J'ai. Le manteau te tient, Mila ? Oui, et les lunettes. Ils avancent vers le seuil, sans courir. La gouttière n'a pas fini. Une maison, avant la dernière goutte. Aniss marche derrière, sans se presser. Un éclat de thym brille, au bord du &lt;emphasis&gt;seau&lt;/emphasis&gt;. [pause]</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -12681,6 +12687,8 @@
 enfant-f|Oui, et les lunettes.
 narrateur|Ils avancent vers le seuil, sans courir.
 papa|La gouttière n'a pas fini.
+enfant-f|Une maison, avant la dernière goutte.
+narrateur|Aniss marche derrière, sans se presser.
 narrateur|Un éclat de thym brille, au bord du seau.</t>
         </is>
       </c>
@@ -17424,7 +17432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17502,6 +17510,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
